--- a/sets/grade7-theme1-set2/questions.xlsx
+++ b/sets/grade7-theme1-set2/questions.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>I am short and slim.</t>
+          <t>I have short black hair.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>He is short and plump with curly hair.</t>
+          <t>He is short with curly brown hair.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A: ______?   B: He is tall and well-built with a moustache.</t>
+          <t>A: ______?   B: He is tall and handsome with a moustache.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>plump</t>
+          <t>rude</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>well-built</t>
+          <t>lazy</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>plump</t>
+          <t>lazy</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>well-built</t>
+          <t>stubborn</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1233,28 +1233,28 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Which word means 'big and strong'?</t>
+          <t>Which word is about HEIGHT?</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>cute</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>well-built</t>
+          <t>medium height</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Think about a strong body.</t>
+          <t>tall, short, ______</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -1285,17 +1285,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>blonde</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>curly</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>plump</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>well-built</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1315,28 +1315,28 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Zehra is slim, but her sister Eda is ______.  (opposite)</t>
+          <t>Doruk is always late, but Beren is always ______.  (opposite)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>rude</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>plump</t>
+          <t>on time</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>lazy</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>a little fat</t>
+          <t>A punctual person is always ______.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>thin</t>
+          <t>rude</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ugly</t>
+          <t>lazy</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1520,28 +1520,28 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Ali is ______ than his brother.  (slim)</t>
+          <t>Nina is ______ than Dave.  (short)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>slimer</t>
+          <t>more short</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>slimmest</t>
+          <t>shortest</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>slimmer</t>
+          <t>shorter</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>slim</t>
+          <t>short</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>big → bigger  (double the last letter)</t>
+          <t>Short word + er:  small → smaller</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -1608,22 +1608,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Dave is heavy than Nina.</t>
+          <t>My grandfather is old than my father.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dave is more heavier than Nina.</t>
+          <t>My grandfather is oldest than my father.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Dave is heavyer than Nina.</t>
+          <t>My grandfather is more old than my father.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Dave is heavier than Nina.</t>
+          <t>My grandfather is older than my father.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>happy → happier</t>
+          <t>Short word + er:  small → smaller</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>

--- a/sets/grade7-theme1-set2/questions.xlsx
+++ b/sets/grade7-theme1-set2/questions.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>youngest</t>
+          <t>young</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>shortest</t>
+          <t>short</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>more shorter</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1567,17 +1567,17 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>more hardworkinger</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>hardworking</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>hardworkinger</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>most hardworking</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1608,17 +1608,17 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>My grandfather is more older than my father.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>My grandfather is more old than my father.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>My grandfather is old than my father.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>My grandfather is oldest than my father.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>My grandfather is more old than my father.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1643,28 +1643,28 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>He is handsome ______ short black hair and brown eyes.</t>
+          <t>He is handsome with short black hair and big brown ______.</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>smile</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>height</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>eyes</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>a boy ______ black hair = a boy who has black hair</t>
+          <t>What can be big and brown on a face?</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -1684,28 +1684,28 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>I don't like him ______ he is very selfish.</t>
+          <t>I don't like him because he is very ______. He is not kind to people.</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>generous</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>because</t>
+          <t>rude</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>This word answers the question 'Why?'</t>
+          <t>Opposite of kind.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -1725,28 +1725,28 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Bora is very generous. ______ he has a lot of friends.</t>
+          <t>Bora always buys gifts for his friends. He is very ______. That's why he has a lot of friends.</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Than</t>
+          <t>selfish</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Because</t>
+          <t>stubborn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>With</t>
+          <t>lazy</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>That's why</t>
+          <t>generous</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>It means 'so'.</t>
+          <t>He likes giving things.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>

--- a/sets/grade7-theme1-set2/questions.xlsx
+++ b/sets/grade7-theme1-set2/questions.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>She wears a headscarf and she has got brown eyes.</t>
+          <t>She has got big brown eyes and a nice smile.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Look at her head and her eyes.</t>
+          <t>Look at her eyes and her mouth.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
